--- a/CostosProyectoconPuntosCU.xlsx
+++ b/CostosProyectoconPuntosCU.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Costos Indirectos" sheetId="1" state="visible" r:id="rId2"/>
@@ -529,7 +529,6 @@
     </font>
     <font>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
     <font>
@@ -979,7 +978,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="116">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -1008,7 +1007,6 @@
     <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1018,15 +1016,9 @@
     <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="164" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="1" applyNumberFormat="1" applyBorder="1" quotePrefix="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1822,7 +1814,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="6">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1836,15 +1828,15 @@
         <v>6</v>
       </c>
       <c r="C4" s="8">
-        <f>D4*12</f>
-        <v>1800000</v>
+        <f t="shared" ref="C4:C9" si="0">D4*12</f>
+        <v>2400000</v>
       </c>
       <c r="D4" s="8">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="E4" s="8">
-        <f t="shared" ref="E4:E19" si="0">+D4/$I$2</f>
-        <v>5769.2307692307695</v>
+        <f t="shared" ref="E4:E19" si="1">+D4/$I$2</f>
+        <v>9523.8095238095229</v>
       </c>
     </row>
     <row r="5">
@@ -1852,15 +1844,15 @@
         <v>7</v>
       </c>
       <c r="C5" s="8">
-        <f>D5*12</f>
+        <f t="shared" si="0"/>
         <v>240000</v>
       </c>
       <c r="D5" s="8">
         <v>20000</v>
       </c>
       <c r="E5" s="8">
-        <f>+D5/$I$2</f>
-        <v>769.23076923076928</v>
+        <f t="shared" si="1"/>
+        <v>952.38095238095241</v>
       </c>
     </row>
     <row r="6">
@@ -1868,15 +1860,15 @@
         <v>8</v>
       </c>
       <c r="C6" s="8">
-        <f>D6*12</f>
-        <v>60000</v>
+        <f t="shared" si="0"/>
+        <v>84000</v>
       </c>
       <c r="D6" s="8">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="E6" s="8">
-        <f>+D6/$I$2</f>
-        <v>192.30769230769232</v>
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
       </c>
     </row>
     <row r="7">
@@ -1884,15 +1876,15 @@
         <v>9</v>
       </c>
       <c r="C7" s="8">
-        <f>D7*12</f>
-        <v>300000</v>
+        <f t="shared" si="0"/>
+        <v>360000</v>
       </c>
       <c r="D7" s="8">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="E7" s="8">
-        <f>+D7/$I$2</f>
-        <v>961.53846153846155</v>
+        <f t="shared" si="1"/>
+        <v>1428.5714285714287</v>
       </c>
     </row>
     <row r="8">
@@ -1900,15 +1892,15 @@
         <v>10</v>
       </c>
       <c r="C8" s="8">
-        <f>D8*12</f>
-        <v>240000</v>
+        <f t="shared" si="0"/>
+        <v>300000</v>
       </c>
       <c r="D8" s="8">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="E8" s="8">
-        <f>+D8/$I$2</f>
-        <v>769.23076923076928</v>
+        <f t="shared" si="1"/>
+        <v>1190.4761904761904</v>
       </c>
     </row>
     <row r="9">
@@ -1916,15 +1908,15 @@
         <v>11</v>
       </c>
       <c r="C9" s="8">
-        <f>D9*12</f>
+        <f t="shared" si="0"/>
         <v>120000</v>
       </c>
       <c r="D9" s="8">
         <v>10000</v>
       </c>
       <c r="E9" s="8">
-        <f>+D9/$I$2</f>
-        <v>384.61538461538464</v>
+        <f t="shared" si="1"/>
+        <v>476.1904761904762</v>
       </c>
     </row>
     <row r="10">
@@ -1932,15 +1924,15 @@
         <v>12</v>
       </c>
       <c r="C10" s="8">
-        <f>D10*12</f>
+        <f t="shared" ref="C10:C11" si="2">D10*12</f>
         <v>360000</v>
       </c>
       <c r="D10" s="8">
         <v>30000</v>
       </c>
       <c r="E10" s="8">
-        <f>+D10/$I$2</f>
-        <v>1153.8461538461538</v>
+        <f t="shared" ref="E10:E11" si="3">+D10/$I$2</f>
+        <v>1428.5714285714287</v>
       </c>
     </row>
     <row r="11">
@@ -1948,15 +1940,15 @@
         <v>13</v>
       </c>
       <c r="C11" s="8">
-        <f>D11*12</f>
-        <v>120000</v>
+        <f t="shared" si="2"/>
+        <v>180000</v>
       </c>
       <c r="D11" s="8">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="E11" s="8">
-        <f>+D11/$I$2</f>
-        <v>384.61538461538464</v>
+        <f t="shared" si="3"/>
+        <v>714.28571428571433</v>
       </c>
     </row>
     <row r="12">
@@ -2007,15 +1999,15 @@
       </c>
       <c r="C19" s="8">
         <f>SUM(C4:C18)</f>
-        <v>3240000</v>
+        <v>4044000</v>
       </c>
       <c r="D19" s="8">
         <f>SUM(D4:D18)</f>
-        <v>270000</v>
+        <v>337000</v>
       </c>
       <c r="E19" s="8">
-        <f t="shared" si="0"/>
-        <v>10384.615384615385</v>
+        <f t="shared" si="1"/>
+        <v>16047.619047619048</v>
       </c>
     </row>
   </sheetData>
@@ -2034,7 +2026,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="2" max="2" style="9" width="52.00390625"/>
-    <col bestFit="1" min="4" max="4" style="1" width="12.00390625"/>
+    <col bestFit="1" min="4" max="4" style="1" width="13.57421875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" style="1" width="17.85546875"/>
     <col bestFit="1" customWidth="1" min="9" max="9" width="28.42578125"/>
   </cols>
@@ -2072,20 +2064,20 @@
         <v>20</v>
       </c>
       <c r="C3" s="15">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D3" s="16">
         <v>60000</v>
       </c>
       <c r="E3" s="16">
-        <f>D3*C3</f>
-        <v>1200000</v>
+        <f t="shared" ref="E3:E7" si="4">D3*C3</f>
+        <v>660000</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="6">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="15">
@@ -2093,14 +2085,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" s="16">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="E4" s="16">
-        <f>D4*C4</f>
-        <v>150000</v>
+        <f t="shared" si="4"/>
+        <v>300000</v>
       </c>
     </row>
     <row r="5" ht="15">
@@ -2111,11 +2103,11 @@
         <v>10</v>
       </c>
       <c r="D5" s="16">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="E5" s="16">
-        <f>D5*C5</f>
-        <v>150000</v>
+        <f t="shared" si="4"/>
+        <v>200000</v>
       </c>
     </row>
     <row r="6" ht="15">
@@ -2126,11 +2118,11 @@
         <v>40</v>
       </c>
       <c r="D6" s="16">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E6" s="16">
-        <f>D6*C6</f>
-        <v>200000</v>
+        <f t="shared" si="4"/>
+        <v>240000</v>
       </c>
     </row>
     <row r="7" ht="15">
@@ -2144,7 +2136,7 @@
         <v>406000</v>
       </c>
       <c r="E7" s="16">
-        <f>D7*C7</f>
+        <f t="shared" si="4"/>
         <v>406000</v>
       </c>
     </row>
@@ -2156,11 +2148,11 @@
         <v>1</v>
       </c>
       <c r="D8" s="16">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="E8" s="16">
         <f>D8*C8*J2</f>
-        <v>1500000</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="9" ht="15">
@@ -2168,14 +2160,14 @@
         <v>27</v>
       </c>
       <c r="C9" s="15">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D9" s="16">
         <v>8000</v>
       </c>
       <c r="E9" s="16">
         <f>D9*C9</f>
-        <v>120000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="10" ht="15">
@@ -2183,14 +2175,14 @@
         <v>28</v>
       </c>
       <c r="C10" s="15">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D10" s="16">
         <v>1500</v>
       </c>
       <c r="E10" s="16">
         <f>D10*C10*J2</f>
-        <v>390000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="11" ht="15">
@@ -2198,14 +2190,14 @@
         <v>29</v>
       </c>
       <c r="C11" s="15">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D11" s="16">
         <v>400</v>
       </c>
       <c r="E11" s="16">
         <f>D11*C11*J2</f>
-        <v>104000</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="12" ht="15">
@@ -2213,14 +2205,14 @@
         <v>30</v>
       </c>
       <c r="C12" s="15">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D12" s="16">
         <v>500</v>
       </c>
       <c r="E12" s="16">
         <f>D12*C12*J2</f>
-        <v>130000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="13" ht="15">
@@ -2240,7 +2232,7 @@
     </row>
     <row r="14">
       <c r="B14" s="14"/>
-      <c r="C14" s="18"/>
+      <c r="C14" s="15"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
     </row>
@@ -2251,14 +2243,14 @@
       <c r="E15" s="16"/>
     </row>
     <row r="16">
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="16"/>
       <c r="E16" s="16">
         <f>SUM(E3:E15)</f>
-        <v>4950000</v>
+        <v>4467000</v>
       </c>
     </row>
   </sheetData>
@@ -2285,14 +2277,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3">
       <c r="B3" s="12" t="s">
@@ -2301,7 +2293,7 @@
       <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="13" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="12" t="s">
@@ -2315,139 +2307,139 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="16">
         <v>70000</v>
       </c>
-      <c r="D4" s="24">
-        <v>4</v>
-      </c>
-      <c r="E4" s="25">
-        <f>C4*D4</f>
-        <v>280000</v>
-      </c>
-      <c r="F4" s="25">
-        <f>E4*G4</f>
-        <v>1680000</v>
-      </c>
-      <c r="G4" s="26">
+      <c r="D4" s="21">
+        <v>3</v>
+      </c>
+      <c r="E4" s="22">
+        <f t="shared" ref="E4:E9" si="5">C4*D4</f>
+        <v>210000</v>
+      </c>
+      <c r="F4" s="22">
+        <f t="shared" ref="F4:F9" si="6">E4*G4</f>
+        <v>1260000</v>
+      </c>
+      <c r="G4" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C5" s="16">
         <v>65000</v>
       </c>
-      <c r="D5" s="24">
-        <v>2</v>
-      </c>
-      <c r="E5" s="25">
-        <f>C5*D5</f>
-        <v>130000</v>
-      </c>
-      <c r="F5" s="25">
-        <f>E5*G5</f>
-        <v>780000</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="D5" s="21">
+        <v>1</v>
+      </c>
+      <c r="E5" s="22">
+        <f t="shared" si="5"/>
+        <v>65000</v>
+      </c>
+      <c r="F5" s="22">
+        <f t="shared" si="6"/>
+        <v>390000</v>
+      </c>
+      <c r="G5" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="16">
         <v>90000</v>
       </c>
       <c r="D6" s="6">
-        <v>2</v>
-      </c>
-      <c r="E6" s="25">
-        <f>C6*D6</f>
-        <v>180000</v>
-      </c>
-      <c r="F6" s="25">
-        <f>E6*G6</f>
-        <v>1800000</v>
-      </c>
-      <c r="G6" s="26">
+        <v>1</v>
+      </c>
+      <c r="E6" s="22">
+        <f t="shared" si="5"/>
+        <v>90000</v>
+      </c>
+      <c r="F6" s="22">
+        <f t="shared" si="6"/>
+        <v>900000</v>
+      </c>
+      <c r="G6" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C7" s="16">
-        <v>80000</v>
-      </c>
-      <c r="D7" s="24">
-        <v>10</v>
-      </c>
-      <c r="E7" s="25">
-        <f>C7*D7</f>
-        <v>800000</v>
-      </c>
-      <c r="F7" s="25">
-        <f>E7*G7</f>
-        <v>6400000</v>
-      </c>
-      <c r="G7" s="26">
+        <v>90000</v>
+      </c>
+      <c r="D7" s="21">
         <v>8</v>
       </c>
+      <c r="E7" s="22">
+        <f t="shared" si="5"/>
+        <v>720000</v>
+      </c>
+      <c r="F7" s="22">
+        <f t="shared" si="6"/>
+        <v>5760000</v>
+      </c>
+      <c r="G7" s="23">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="16">
-        <v>65000</v>
-      </c>
-      <c r="D8" s="24">
+        <v>70000</v>
+      </c>
+      <c r="D8" s="21">
         <v>5</v>
       </c>
-      <c r="E8" s="25">
-        <f>C8*D8</f>
-        <v>325000</v>
-      </c>
-      <c r="F8" s="25">
-        <f>E8*G8</f>
-        <v>2600000</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="E8" s="22">
+        <f t="shared" si="5"/>
+        <v>350000</v>
+      </c>
+      <c r="F8" s="22">
+        <f t="shared" si="6"/>
+        <v>2800000</v>
+      </c>
+      <c r="G8" s="23">
         <v>8</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="16">
-        <v>120000</v>
+        <v>140000</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
       </c>
-      <c r="E9" s="25">
-        <f>C9*D9</f>
-        <v>120000</v>
-      </c>
-      <c r="F9" s="25">
-        <f>E9*G9</f>
-        <v>1200000</v>
-      </c>
-      <c r="G9" s="26">
+      <c r="E9" s="22">
+        <f t="shared" si="5"/>
+        <v>140000</v>
+      </c>
+      <c r="F9" s="22">
+        <f t="shared" si="6"/>
+        <v>1400000</v>
+      </c>
+      <c r="G9" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="16">
@@ -2456,18 +2448,18 @@
       <c r="D10" s="6">
         <v>0</v>
       </c>
-      <c r="E10" s="25">
-        <f>C10*D10</f>
+      <c r="E10" s="22">
+        <f t="shared" ref="E10:E13" si="7">C10*D10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="25">
-        <f>E10*G10</f>
+      <c r="F10" s="22">
+        <f t="shared" ref="F10:F13" si="8">E10*G10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="23"/>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="16">
@@ -2476,20 +2468,20 @@
       <c r="D11" s="6">
         <v>1</v>
       </c>
-      <c r="E11" s="25">
-        <f>C11*D11</f>
+      <c r="E11" s="22">
+        <f t="shared" si="7"/>
         <v>85000</v>
       </c>
-      <c r="F11" s="25">
-        <f>E11*G11</f>
+      <c r="F11" s="22">
+        <f t="shared" si="8"/>
         <v>850000</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C12" s="16">
@@ -2498,18 +2490,18 @@
       <c r="D12" s="6">
         <v>0</v>
       </c>
-      <c r="E12" s="25">
-        <f>C12*D12</f>
+      <c r="E12" s="22">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F12" s="25">
-        <f>E12*G12</f>
+      <c r="F12" s="22">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="23"/>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C13" s="16">
@@ -2518,33 +2510,33 @@
       <c r="D13" s="6">
         <v>1</v>
       </c>
-      <c r="E13" s="25">
-        <f>C13*D13</f>
+      <c r="E13" s="22">
+        <f t="shared" si="7"/>
         <v>90000</v>
       </c>
-      <c r="F13" s="25">
-        <f>E13*G13</f>
+      <c r="F13" s="22">
+        <f t="shared" si="8"/>
         <v>720000</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="23">
         <v>8</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="23"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="16"/>
       <c r="D14" s="6"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="26"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="23"/>
     </row>
     <row r="15">
-      <c r="B15" s="23"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="16"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="26"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="23"/>
     </row>
     <row r="16">
       <c r="B16" s="6"/>
@@ -2552,7 +2544,7 @@
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="26"/>
+      <c r="G16" s="23"/>
     </row>
     <row r="17">
       <c r="B17" s="6"/>
@@ -2560,26 +2552,26 @@
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="26"/>
+      <c r="G17" s="23"/>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C18" s="16"/>
-      <c r="D18" s="24">
+      <c r="D18" s="21">
         <f>SUM(D4:D17)</f>
-        <v>26</v>
-      </c>
-      <c r="E18" s="25">
+        <v>21</v>
+      </c>
+      <c r="E18" s="22">
         <f>SUM(E4:E17)</f>
-        <v>2010000</v>
-      </c>
-      <c r="F18" s="25">
+        <v>1750000</v>
+      </c>
+      <c r="F18" s="22">
         <f>SUM(F4:F17)</f>
-        <v>16030000</v>
-      </c>
-      <c r="G18" s="25"/>
+        <v>14080000</v>
+      </c>
+      <c r="G18" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2597,8 +2589,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="2" max="2" width="24.7109375"/>
-    <col bestFit="1" min="4" max="4" style="1" width="12.00390625"/>
-    <col bestFit="1" min="5" max="5" style="1" width="13.57421875"/>
+    <col bestFit="1" min="4" max="5" style="1" width="13.57421875"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -2631,11 +2622,11 @@
         <v>6</v>
       </c>
       <c r="D4" s="16">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="E4" s="16">
-        <f t="shared" ref="E4:E5" si="1">+D4*C4</f>
-        <v>720000</v>
+        <f t="shared" ref="E4:E9" si="9">+D4*C4</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="5">
@@ -2646,11 +2637,11 @@
         <v>1</v>
       </c>
       <c r="D5" s="16">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="E5" s="16">
-        <f t="shared" si="1"/>
-        <v>800000</v>
+        <f t="shared" si="9"/>
+        <v>1000000</v>
       </c>
     </row>
     <row r="6">
@@ -2664,7 +2655,7 @@
         <v>500000</v>
       </c>
       <c r="E6" s="16">
-        <f>+D6*C6</f>
+        <f t="shared" si="9"/>
         <v>500000</v>
       </c>
     </row>
@@ -2676,11 +2667,11 @@
         <v>40</v>
       </c>
       <c r="D7" s="16">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="E7" s="16">
-        <f>+D7*C7</f>
-        <v>240000</v>
+        <f t="shared" si="9"/>
+        <v>400000</v>
       </c>
     </row>
     <row r="8">
@@ -2691,26 +2682,26 @@
         <v>1</v>
       </c>
       <c r="D8" s="16">
-        <v>300000</v>
+        <v>700000</v>
       </c>
       <c r="E8" s="16">
-        <f>+D8*C8</f>
-        <v>300000</v>
+        <f t="shared" si="9"/>
+        <v>700000</v>
       </c>
     </row>
     <row r="9" ht="15">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="6">
         <v>8</v>
       </c>
       <c r="D9" s="16">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="E9" s="16">
-        <f>+D9*C9</f>
-        <v>360000</v>
+        <f t="shared" si="9"/>
+        <v>480000</v>
       </c>
     </row>
     <row r="10">
@@ -2721,7 +2712,7 @@
       <c r="D10" s="16"/>
       <c r="E10" s="16">
         <f>SUM(E4:E9)</f>
-        <v>2920000</v>
+        <v>3980000</v>
       </c>
     </row>
   </sheetData>
@@ -2745,10 +2736,10 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="20"/>
     </row>
     <row r="3">
       <c r="B3" s="12" t="s">
@@ -2770,7 +2761,7 @@
       </c>
       <c r="C4" s="16">
         <f>+'Costos Indirectos'!E19*'Hw&amp;SW'!J3*'Hw&amp;SW'!J2</f>
-        <v>2700000</v>
+        <v>3370000</v>
       </c>
     </row>
     <row r="5">
@@ -2779,7 +2770,7 @@
       </c>
       <c r="C5" s="16">
         <f>+'Hw&amp;SW'!E16</f>
-        <v>4950000</v>
+        <v>4467000</v>
       </c>
     </row>
     <row r="6">
@@ -2788,7 +2779,7 @@
       </c>
       <c r="C6" s="16">
         <f>+Sueldos!F18</f>
-        <v>16030000</v>
+        <v>14080000</v>
       </c>
     </row>
     <row r="7">
@@ -2797,7 +2788,7 @@
       </c>
       <c r="C7" s="16">
         <f>+Otros!E10</f>
-        <v>2920000</v>
+        <v>3980000</v>
       </c>
     </row>
     <row r="8">
@@ -2806,7 +2797,7 @@
       </c>
       <c r="C8" s="16">
         <f>SUM(C4:C6)</f>
-        <v>23680000</v>
+        <v>21917000</v>
       </c>
     </row>
     <row r="9">
@@ -2815,11 +2806,11 @@
       </c>
       <c r="C9" s="16">
         <f>B15-C8</f>
-        <v>10114760</v>
+        <v>11877760</v>
       </c>
       <c r="D9" s="6">
         <f>C9/B15</f>
-        <v>0.29929965473937381</v>
+        <v>0.35146750561329626</v>
       </c>
       <c r="E9" s="6"/>
     </row>
@@ -2832,21 +2823,21 @@
         <v>33794760</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="24">
+      <c r="E10" s="21">
         <f>+DistribuciónEsfuerzo!C23</f>
-        <v>7.0072694999999978</v>
+        <v>7.5345654999999985</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="12" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="24" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="6">
@@ -2854,7 +2845,7 @@
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="B15" s="29">
+      <c r="B15" s="24">
         <v>33794760</v>
       </c>
       <c r="C15" s="6"/>
@@ -2872,865 +2863,865 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" style="9" width="46.5703125"/>
-    <col customWidth="1" min="2" max="2" style="30" width="39.42578125"/>
-    <col customWidth="1" min="3" max="3" style="31" width="10.42578125"/>
-    <col customWidth="1" min="4" max="4" style="32" width="15.5703125"/>
+    <col customWidth="1" min="2" max="2" style="25" width="39.42578125"/>
+    <col customWidth="1" min="3" max="3" style="26" width="10.42578125"/>
+    <col customWidth="1" min="4" max="4" style="27" width="15.5703125"/>
     <col customWidth="1" min="5" max="5" width="15.5703125"/>
-    <col customWidth="1" min="6" max="6" style="32" width="26.85546875"/>
+    <col customWidth="1" min="6" max="6" style="27" width="26.85546875"/>
     <col customWidth="1" min="7" max="7" width="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="2" ht="15.75">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="37"/>
-    </row>
-    <row r="3" s="39" customFormat="1" ht="13.5">
-      <c r="A3" s="40" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="32"/>
+    </row>
+    <row r="3" s="34" customFormat="1" ht="13.5">
+      <c r="A3" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="40" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="48">
+      <c r="C4" s="43">
         <v>1</v>
       </c>
-      <c r="D4" s="49">
+      <c r="D4" s="44">
         <v>2</v>
       </c>
-      <c r="E4" s="50">
-        <f t="shared" ref="E4:E6" si="2">C4*D4</f>
+      <c r="E4" s="45">
+        <f t="shared" ref="E4:E6" si="10">C4*D4</f>
         <v>2</v>
       </c>
-      <c r="F4" s="51"/>
+      <c r="F4" s="46"/>
     </row>
     <row r="5">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="49">
         <v>2</v>
       </c>
-      <c r="D5" s="55">
+      <c r="D5" s="50">
+        <v>3</v>
+      </c>
+      <c r="E5" s="51">
+        <f t="shared" si="10"/>
+        <v>6</v>
+      </c>
+      <c r="F5" s="52"/>
+    </row>
+    <row r="6" ht="15.75">
+      <c r="A6" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="55">
+        <v>3</v>
+      </c>
+      <c r="D6" s="56">
+        <v>5</v>
+      </c>
+      <c r="E6" s="57">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="F6" s="58"/>
+    </row>
+    <row r="7" ht="15.75">
+      <c r="A7" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="39">
+        <f>SUM(E4:E6)</f>
+        <v>23</v>
+      </c>
+      <c r="F7" s="60"/>
+    </row>
+    <row r="8" ht="15.75">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="32"/>
+    </row>
+    <row r="9" s="34" customFormat="1" ht="25.5">
+      <c r="A9" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="36"/>
+      <c r="C9" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="43">
+        <v>5</v>
+      </c>
+      <c r="D10" s="44">
+        <v>1</v>
+      </c>
+      <c r="E10" s="45">
+        <f t="shared" ref="E10:E12" si="11">C10*D10</f>
+        <v>5</v>
+      </c>
+      <c r="F10" s="46"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="49">
+        <v>10</v>
+      </c>
+      <c r="D11" s="50">
+        <v>9</v>
+      </c>
+      <c r="E11" s="51">
+        <f t="shared" si="11"/>
+        <v>90</v>
+      </c>
+      <c r="F11" s="52"/>
+    </row>
+    <row r="12" ht="15.75">
+      <c r="A12" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="55">
+        <v>15</v>
+      </c>
+      <c r="D12" s="56">
+        <v>0</v>
+      </c>
+      <c r="E12" s="57">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="58"/>
+    </row>
+    <row r="13" ht="15.75">
+      <c r="A13" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="39">
+        <f>SUM(E10:E12)</f>
+        <v>95</v>
+      </c>
+      <c r="F13" s="60"/>
+    </row>
+    <row r="14" ht="15.75">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="32"/>
+    </row>
+    <row r="15" ht="15.75">
+      <c r="A15" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="65">
+        <f>TAW+TBF</f>
+        <v>118</v>
+      </c>
+      <c r="F15" s="66"/>
+    </row>
+    <row r="16" ht="15.75">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="32"/>
+    </row>
+    <row r="17" s="34" customFormat="1" ht="13.5">
+      <c r="A17" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="67">
         <v>2</v>
       </c>
-      <c r="E5" s="56">
-        <f t="shared" si="2"/>
+      <c r="D18" s="44">
+        <v>5</v>
+      </c>
+      <c r="E18" s="45">
+        <f t="shared" ref="E18:E30" si="12">C18*D18</f>
+        <v>10</v>
+      </c>
+      <c r="F18" s="46"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="68">
+        <v>1</v>
+      </c>
+      <c r="D19" s="50">
         <v>4</v>
       </c>
-      <c r="F5" s="57"/>
-    </row>
-    <row r="6" ht="15.75">
-      <c r="A6" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="60">
+      <c r="E19" s="51">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="F19" s="52"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="68">
+        <v>1</v>
+      </c>
+      <c r="D20" s="50">
+        <v>5</v>
+      </c>
+      <c r="E20" s="51">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="F20" s="52"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="68">
+        <v>1</v>
+      </c>
+      <c r="D21" s="50">
+        <v>4</v>
+      </c>
+      <c r="E21" s="51">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="F21" s="52"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="68">
+        <v>1</v>
+      </c>
+      <c r="D22" s="50">
+        <v>5</v>
+      </c>
+      <c r="E22" s="51">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="F22" s="52"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="50">
         <v>3</v>
       </c>
-      <c r="D6" s="61">
+      <c r="E23" s="51">
+        <f t="shared" si="12"/>
+        <v>1.5</v>
+      </c>
+      <c r="F23" s="52"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="50">
         <v>5</v>
       </c>
-      <c r="E6" s="62">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="F6" s="63"/>
-    </row>
-    <row r="7" ht="15.75">
-      <c r="A7" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="44">
-        <f>SUM(E4:E6)</f>
-        <v>21</v>
-      </c>
-      <c r="F7" s="65"/>
-    </row>
-    <row r="8" ht="15.75">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="37"/>
-    </row>
-    <row r="9" s="39" customFormat="1" ht="26.25">
-      <c r="A9" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="48">
+      <c r="E24" s="51">
+        <f t="shared" si="12"/>
+        <v>2.5</v>
+      </c>
+      <c r="F24" s="52"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="68">
+        <v>2</v>
+      </c>
+      <c r="D25" s="50">
+        <v>4</v>
+      </c>
+      <c r="E25" s="51">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="F25" s="52"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="68">
+        <v>1</v>
+      </c>
+      <c r="D26" s="50">
         <v>5</v>
       </c>
-      <c r="D10" s="49">
-        <v>3</v>
-      </c>
-      <c r="E10" s="50">
-        <f t="shared" ref="E10:E12" si="3">C10*D10</f>
-        <v>15</v>
-      </c>
-      <c r="F10" s="51"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="54">
-        <v>10</v>
-      </c>
-      <c r="D11" s="55">
-        <v>3</v>
-      </c>
-      <c r="E11" s="56">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="F11" s="57"/>
-    </row>
-    <row r="12" ht="15.75">
-      <c r="A12" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="60">
-        <v>15</v>
-      </c>
-      <c r="D12" s="61">
-        <v>4</v>
-      </c>
-      <c r="E12" s="62">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="F12" s="63"/>
-    </row>
-    <row r="13" ht="15.75">
-      <c r="A13" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="44">
-        <f>SUM(E10:E12)</f>
-        <v>105</v>
-      </c>
-      <c r="F13" s="65"/>
-    </row>
-    <row r="14" ht="15.75">
-      <c r="A14" s="34"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="37"/>
-    </row>
-    <row r="15" ht="15.75">
-      <c r="A15" s="66" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="70">
-        <f>TAW+TBF</f>
-        <v>126</v>
-      </c>
-      <c r="F15" s="71"/>
-    </row>
-    <row r="16" ht="15.75">
-      <c r="A16" s="34"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="37"/>
-    </row>
-    <row r="17" s="39" customFormat="1" ht="13.5">
-      <c r="A17" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="45" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="47" t="s">
+      <c r="E26" s="51">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="F26" s="52"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="72">
-        <v>2</v>
-      </c>
-      <c r="D18" s="49">
+      <c r="C27" s="68">
+        <v>1</v>
+      </c>
+      <c r="D27" s="50">
         <v>5</v>
       </c>
-      <c r="E18" s="50">
-        <f t="shared" ref="E18:E30" si="4">C18*D18</f>
-        <v>10</v>
-      </c>
-      <c r="F18" s="51"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="53" t="s">
+      <c r="E27" s="51">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="F27" s="52"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="73">
+      <c r="C28" s="68">
         <v>1</v>
       </c>
-      <c r="D19" s="55">
-        <v>4</v>
-      </c>
-      <c r="E19" s="56">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="F19" s="57"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="53" t="s">
+      <c r="D28" s="50">
+        <v>5</v>
+      </c>
+      <c r="E28" s="51">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="F28" s="52"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="73">
+      <c r="C29" s="68">
         <v>1</v>
       </c>
-      <c r="D20" s="55">
+      <c r="D29" s="50">
         <v>5</v>
       </c>
-      <c r="E20" s="56">
-        <f t="shared" si="4"/>
+      <c r="E29" s="51">
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="F20" s="57"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="53" t="s">
+      <c r="F29" s="52"/>
+    </row>
+    <row r="30" ht="25.5">
+      <c r="A30" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="73">
+      <c r="C30" s="69">
         <v>1</v>
       </c>
-      <c r="D21" s="55">
-        <v>4</v>
-      </c>
-      <c r="E21" s="56">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="F21" s="57"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="52" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="73">
-        <v>1</v>
-      </c>
-      <c r="D22" s="55">
-        <v>5</v>
-      </c>
-      <c r="E22" s="56">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="F22" s="57"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="73">
-        <v>0.5</v>
-      </c>
-      <c r="D23" s="55">
-        <v>3</v>
-      </c>
-      <c r="E23" s="56">
-        <f t="shared" si="4"/>
-        <v>1.5</v>
-      </c>
-      <c r="F23" s="57"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="73">
-        <v>0.5</v>
-      </c>
-      <c r="D24" s="55">
-        <v>5</v>
-      </c>
-      <c r="E24" s="56">
-        <f t="shared" si="4"/>
-        <v>2.5</v>
-      </c>
-      <c r="F24" s="57"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="73">
-        <v>2</v>
-      </c>
-      <c r="D25" s="55">
-        <v>4</v>
-      </c>
-      <c r="E25" s="56">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="F25" s="57"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="73">
-        <v>1</v>
-      </c>
-      <c r="D26" s="55">
-        <v>5</v>
-      </c>
-      <c r="E26" s="56">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="F26" s="57"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="73">
-        <v>1</v>
-      </c>
-      <c r="D27" s="55">
-        <v>5</v>
-      </c>
-      <c r="E27" s="56">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="F27" s="57"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="73">
-        <v>1</v>
-      </c>
-      <c r="D28" s="55">
-        <v>5</v>
-      </c>
-      <c r="E28" s="56">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="F28" s="57"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="52" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="73">
-        <v>1</v>
-      </c>
-      <c r="D29" s="55">
-        <v>5</v>
-      </c>
-      <c r="E29" s="56">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="F29" s="57"/>
-    </row>
-    <row r="30" ht="27">
-      <c r="A30" s="58" t="s">
-        <v>102</v>
-      </c>
-      <c r="B30" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" s="74">
-        <v>1</v>
-      </c>
-      <c r="D30" s="61">
+      <c r="D30" s="56">
         <v>0</v>
       </c>
-      <c r="E30" s="62">
-        <f t="shared" si="4"/>
+      <c r="E30" s="57">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="F30" s="63"/>
+      <c r="F30" s="58"/>
     </row>
     <row r="31" ht="15.75">
-      <c r="A31" s="40" t="s">
+      <c r="A31" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="75">
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="70">
         <f>SUM(E18:E30)</f>
         <v>60</v>
       </c>
-      <c r="F31" s="65"/>
+      <c r="F31" s="60"/>
     </row>
     <row r="32" ht="15.75">
-      <c r="A32" s="76" t="s">
+      <c r="A32" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="77" t="s">
+      <c r="B32" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="C32" s="78"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="80">
+      <c r="C32" s="73"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="75">
         <f>0.01*E31+0.06</f>
         <v>0.65999999999999992</v>
       </c>
-      <c r="F32" s="81"/>
+      <c r="F32" s="76"/>
     </row>
     <row r="33" ht="15.75">
-      <c r="A33" s="34"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="37"/>
-    </row>
-    <row r="34" s="39" customFormat="1" ht="26.25">
-      <c r="A34" s="40" t="s">
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="32"/>
+    </row>
+    <row r="34" s="34" customFormat="1" ht="25.5">
+      <c r="A34" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="42" t="s">
+      <c r="C34" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="43" t="s">
+      <c r="D34" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="E34" s="44" t="s">
+      <c r="E34" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="43" t="s">
+      <c r="F34" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="G34" s="45" t="s">
+      <c r="G34" s="40" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="82" t="s">
+      <c r="A35" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="72">
+      <c r="C35" s="67">
         <v>1.5</v>
       </c>
-      <c r="D35" s="49">
+      <c r="D35" s="44">
         <v>3</v>
       </c>
-      <c r="E35" s="50">
-        <f t="shared" ref="E35:E42" si="5">C35*D35</f>
+      <c r="E35" s="45">
+        <f t="shared" ref="E35:E42" si="13">C35*D35</f>
         <v>4.5</v>
       </c>
-      <c r="F35" s="49"/>
-      <c r="G35" s="83">
-        <f t="shared" ref="G35:G40" si="6">IF(E35&lt;3,1,0)</f>
+      <c r="F35" s="44"/>
+      <c r="G35" s="78">
+        <f t="shared" ref="G35:G40" si="14">IF(E35&lt;3,1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="53" t="s">
+      <c r="B36" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="C36" s="73">
+      <c r="C36" s="68">
         <v>0.5</v>
       </c>
-      <c r="D36" s="55">
+      <c r="D36" s="50">
         <v>3</v>
       </c>
-      <c r="E36" s="56">
-        <f t="shared" si="5"/>
+      <c r="E36" s="51">
+        <f t="shared" si="13"/>
         <v>1.5</v>
       </c>
-      <c r="F36" s="55"/>
+      <c r="F36" s="50"/>
       <c r="G36" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="84" t="s">
+      <c r="A37" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="B37" s="53" t="s">
+      <c r="B37" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="73">
+      <c r="C37" s="68">
         <v>1</v>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="50">
         <v>2</v>
       </c>
-      <c r="E37" s="56">
-        <f t="shared" si="5"/>
+      <c r="E37" s="51">
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="F37" s="55"/>
+      <c r="F37" s="50"/>
       <c r="G37" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="84" t="s">
+      <c r="A38" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="53" t="s">
+      <c r="B38" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="C38" s="73">
+      <c r="C38" s="68">
         <v>0.5</v>
       </c>
-      <c r="D38" s="55">
+      <c r="D38" s="50">
         <v>4</v>
       </c>
-      <c r="E38" s="56">
-        <f t="shared" si="5"/>
+      <c r="E38" s="51">
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="F38" s="55"/>
+      <c r="F38" s="50"/>
       <c r="G38" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="84" t="s">
+      <c r="A39" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="53" t="s">
+      <c r="B39" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="73">
+      <c r="C39" s="68">
         <v>1</v>
       </c>
-      <c r="D39" s="55">
+      <c r="D39" s="50">
         <v>5</v>
       </c>
-      <c r="E39" s="56">
-        <f t="shared" si="5"/>
+      <c r="E39" s="51">
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="F39" s="55"/>
+      <c r="F39" s="50"/>
       <c r="G39" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="84" t="s">
+      <c r="A40" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="C40" s="73">
+      <c r="C40" s="68">
         <v>2</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D40" s="50">
         <v>2</v>
       </c>
-      <c r="E40" s="56">
-        <f t="shared" si="5"/>
+      <c r="E40" s="51">
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="F40" s="55"/>
+      <c r="F40" s="50"/>
       <c r="G40" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="84" t="s">
+      <c r="A41" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="53" t="s">
+      <c r="B41" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="C41" s="73">
+      <c r="C41" s="68">
         <v>-1</v>
       </c>
-      <c r="D41" s="55">
+      <c r="D41" s="50">
         <v>5</v>
       </c>
-      <c r="E41" s="56">
-        <f t="shared" si="5"/>
+      <c r="E41" s="51">
+        <f t="shared" si="13"/>
         <v>-5</v>
       </c>
-      <c r="F41" s="55"/>
+      <c r="F41" s="50"/>
       <c r="G41" s="6">
-        <f t="shared" ref="G41:G42" si="7">IF(E41&gt;3,1,0)</f>
+        <f t="shared" ref="G41:G42" si="15">IF(E41&gt;3,1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" ht="15.75">
-      <c r="A42" s="85" t="s">
+      <c r="A42" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="59" t="s">
+      <c r="B42" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="C42" s="74" t="s">
+      <c r="C42" s="69" t="s">
         <v>122</v>
       </c>
-      <c r="D42" s="61">
+      <c r="D42" s="56">
         <v>3</v>
       </c>
-      <c r="E42" s="62">
-        <f t="shared" si="5"/>
+      <c r="E42" s="57">
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
-      <c r="F42" s="61"/>
-      <c r="G42" s="86">
-        <f t="shared" si="7"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="81">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" ht="15.75">
-      <c r="A43" s="40" t="s">
+      <c r="A43" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="B43" s="41"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="75">
+      <c r="B43" s="36"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="70">
         <f>SUM(E35:E42)</f>
         <v>11</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="87">
+      <c r="F43" s="59"/>
+      <c r="G43" s="82">
         <f>SUM(G35:G42)</f>
         <v>3</v>
       </c>
     </row>
     <row r="44" ht="15.75">
-      <c r="A44" s="40" t="s">
+      <c r="A44" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="B44" s="41" t="s">
+      <c r="B44" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="75">
+      <c r="C44" s="37"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="70">
         <f>1.4 + (-0.03*E43)</f>
         <v>1.0699999999999998</v>
       </c>
-      <c r="F44" s="88"/>
-      <c r="G44" s="87"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="82"/>
     </row>
     <row r="45" ht="15.75">
-      <c r="A45" s="34"/>
-      <c r="B45" s="35"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="37"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="32"/>
     </row>
     <row r="46">
-      <c r="A46" s="89" t="s">
+      <c r="A46" s="84" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="90"/>
-      <c r="C46" s="91"/>
-      <c r="D46" s="92"/>
-      <c r="E46" s="93">
+      <c r="B46" s="85"/>
+      <c r="C46" s="86"/>
+      <c r="D46" s="87"/>
+      <c r="E46" s="88">
         <f>UUCP * TCF *EF</f>
-        <v>88.981199999999987</v>
-      </c>
-      <c r="F46" s="94"/>
+        <v>83.33159999999998</v>
+      </c>
+      <c r="F46" s="89"/>
     </row>
     <row r="47">
-      <c r="A47" s="95" t="s">
+      <c r="A47" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="B47" s="96"/>
-      <c r="C47" s="97"/>
-      <c r="D47" s="98"/>
-      <c r="E47" s="99">
+      <c r="B47" s="91"/>
+      <c r="C47" s="92"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="94">
         <v>40</v>
       </c>
-      <c r="F47" s="100"/>
+      <c r="F47" s="95"/>
     </row>
     <row r="48" ht="15.75">
-      <c r="A48" s="95" t="s">
+      <c r="A48" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="B48" s="96"/>
-      <c r="C48" s="97"/>
-      <c r="D48" s="98"/>
-      <c r="E48" s="101">
+      <c r="B48" s="91"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="93"/>
+      <c r="E48" s="96">
         <f>E46*E47</f>
-        <v>3559.2479999999996</v>
-      </c>
-      <c r="F48" s="100"/>
+        <v>3333.2639999999992</v>
+      </c>
+      <c r="F48" s="95"/>
     </row>
     <row r="49">
-      <c r="A49" s="95" t="s">
+      <c r="A49" s="90" t="s">
         <v>129</v>
       </c>
-      <c r="B49" s="96"/>
-      <c r="C49" s="97"/>
-      <c r="D49" s="98"/>
-      <c r="E49" s="102">
+      <c r="B49" s="91"/>
+      <c r="C49" s="92"/>
+      <c r="D49" s="93"/>
+      <c r="E49" s="97">
         <v>0.40000000000000002</v>
       </c>
-      <c r="F49" s="100" t="s">
+      <c r="F49" s="95" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="50" ht="15.75">
-      <c r="A50" s="103" t="s">
+      <c r="A50" s="98" t="s">
         <v>131</v>
       </c>
-      <c r="B50" s="104"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="106"/>
-      <c r="E50" s="101">
+      <c r="B50" s="99"/>
+      <c r="C50" s="100"/>
+      <c r="D50" s="101"/>
+      <c r="E50" s="96">
         <f>E48*(1+E49)</f>
-        <v>4982.9471999999987</v>
-      </c>
-      <c r="F50" s="107"/>
+        <v>4666.5695999999989</v>
+      </c>
+      <c r="F50" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3749,42 +3740,42 @@
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="20.42578125"/>
     <col bestFit="1" customWidth="1" min="2" max="2" width="11.7109375"/>
-    <col customWidth="1" min="3" max="3" style="108" width="13.5703125"/>
+    <col customWidth="1" min="3" max="3" style="103" width="13.5703125"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="19.5703125"/>
     <col bestFit="1" customWidth="1" min="8" max="8" width="18.140625"/>
     <col bestFit="1" customWidth="1" min="10" max="10" width="17.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="104" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2">
-      <c r="A2" s="111" t="s">
+      <c r="A2" s="106" t="s">
         <v>133</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="112" t="s">
+      <c r="C2" s="107" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="106" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="F2" s="106" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="111" t="s">
+      <c r="G2" s="106" t="s">
         <v>138</v>
       </c>
-      <c r="H2" s="111" t="s">
+      <c r="H2" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="I2" s="111" t="s">
+      <c r="I2" s="106" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3792,285 +3783,285 @@
       <c r="A3" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="113">
+      <c r="B3" s="108">
         <v>0.25</v>
       </c>
-      <c r="C3" s="114">
+      <c r="C3" s="109">
         <f>+C7*B3</f>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="E3" s="114">
-        <f t="shared" ref="E3:E10" si="8">+$C$7</f>
-        <v>4982.9471999999987</v>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="E3" s="109">
+        <f t="shared" ref="E3:E10" si="16">+$C$7</f>
+        <v>4666.5695999999989</v>
       </c>
       <c r="F3" s="6">
         <v>160</v>
       </c>
       <c r="G3" s="6">
-        <f t="shared" ref="G3:G10" si="9">+E3/F3</f>
-        <v>31.143419999999992</v>
+        <f t="shared" ref="G3:G10" si="17">+E3/F3</f>
+        <v>29.166059999999995</v>
       </c>
       <c r="H3" s="6">
         <v>2</v>
       </c>
       <c r="I3" s="6">
-        <f t="shared" ref="I3:I10" si="10">+G3/H3</f>
-        <v>15.571709999999996</v>
+        <f t="shared" ref="I3:I10" si="18">+G3/H3</f>
+        <v>14.583029999999997</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="113">
+      <c r="B4" s="108">
         <v>0.20000000000000001</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="109">
         <f>+C7*B4</f>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="E4" s="114">
-        <f t="shared" si="8"/>
-        <v>4982.9471999999987</v>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="E4" s="109">
+        <f t="shared" si="16"/>
+        <v>4666.5695999999989</v>
       </c>
       <c r="F4" s="6">
         <v>160</v>
       </c>
       <c r="G4" s="6">
-        <f t="shared" si="9"/>
-        <v>31.143419999999992</v>
+        <f t="shared" si="17"/>
+        <v>29.166059999999995</v>
       </c>
       <c r="H4" s="6">
         <v>3</v>
       </c>
       <c r="I4" s="6">
-        <f t="shared" si="10"/>
-        <v>10.381139999999997</v>
+        <f t="shared" si="18"/>
+        <v>9.7220199999999988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="108">
         <v>0.34999999999999998</v>
       </c>
-      <c r="C5" s="114">
+      <c r="C5" s="109">
         <f>+C7*B5</f>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="E5" s="114">
-        <f t="shared" si="8"/>
-        <v>4982.9471999999987</v>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="E5" s="109">
+        <f t="shared" si="16"/>
+        <v>4666.5695999999989</v>
       </c>
       <c r="F5" s="6">
         <v>160</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="9"/>
-        <v>31.143419999999992</v>
+        <f t="shared" si="17"/>
+        <v>29.166059999999995</v>
       </c>
       <c r="H5" s="6">
         <v>4</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" si="10"/>
-        <v>7.785854999999998</v>
+        <f t="shared" si="18"/>
+        <v>7.2915149999999986</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="113">
+      <c r="B6" s="108">
         <v>0.20000000000000001</v>
       </c>
-      <c r="C6" s="114">
+      <c r="C6" s="109">
         <f>+C7*B6</f>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="E6" s="114">
-        <f t="shared" si="8"/>
-        <v>4982.9471999999987</v>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="E6" s="109">
+        <f t="shared" si="16"/>
+        <v>4666.5695999999989</v>
       </c>
       <c r="F6" s="6">
         <v>160</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" si="9"/>
-        <v>31.143419999999992</v>
+        <f t="shared" si="17"/>
+        <v>29.166059999999995</v>
       </c>
       <c r="H6" s="6">
         <v>5</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" si="10"/>
-        <v>6.2286839999999986</v>
+        <f t="shared" si="18"/>
+        <v>5.8332119999999987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="113">
+      <c r="B7" s="108">
         <f>SUM(B3:B6)</f>
         <v>1</v>
       </c>
-      <c r="C7" s="115">
+      <c r="C7" s="110">
         <f>+UUCP!E50</f>
-        <v>4982.9471999999987</v>
-      </c>
-      <c r="E7" s="114">
-        <f t="shared" si="8"/>
-        <v>4982.9471999999987</v>
+        <v>4666.5695999999989</v>
+      </c>
+      <c r="E7" s="109">
+        <f t="shared" si="16"/>
+        <v>4666.5695999999989</v>
       </c>
       <c r="F7" s="6">
         <v>160</v>
       </c>
       <c r="G7" s="6">
-        <f t="shared" si="9"/>
-        <v>31.143419999999992</v>
+        <f t="shared" si="17"/>
+        <v>29.166059999999995</v>
       </c>
       <c r="H7" s="6">
         <v>6</v>
       </c>
       <c r="I7" s="6">
-        <f t="shared" si="10"/>
-        <v>5.1905699999999984</v>
+        <f t="shared" si="18"/>
+        <v>4.8610099999999994</v>
       </c>
     </row>
     <row r="8">
-      <c r="E8" s="114">
-        <f t="shared" si="8"/>
-        <v>4982.9471999999987</v>
+      <c r="E8" s="109">
+        <f t="shared" si="16"/>
+        <v>4666.5695999999989</v>
       </c>
       <c r="F8" s="6">
         <v>160</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" si="9"/>
-        <v>31.143419999999992</v>
+        <f t="shared" si="17"/>
+        <v>29.166059999999995</v>
       </c>
       <c r="H8" s="6">
         <v>7</v>
       </c>
       <c r="I8" s="6">
-        <f t="shared" si="10"/>
-        <v>4.4490599999999985</v>
+        <f t="shared" si="18"/>
+        <v>4.1665799999999988</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="E9" s="114">
-        <f t="shared" si="8"/>
-        <v>4982.9471999999987</v>
+      <c r="E9" s="109">
+        <f t="shared" si="16"/>
+        <v>4666.5695999999989</v>
       </c>
       <c r="F9" s="6">
         <v>160</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="9"/>
-        <v>31.143419999999992</v>
+        <f t="shared" si="17"/>
+        <v>29.166059999999995</v>
       </c>
       <c r="H9" s="6">
         <v>8</v>
       </c>
       <c r="I9" s="6">
-        <f t="shared" si="10"/>
-        <v>3.892927499999999</v>
+        <f t="shared" si="18"/>
+        <v>3.6457574999999993</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="94" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="94" t="s">
         <v>146</v>
       </c>
-      <c r="E10" s="114">
-        <f t="shared" si="8"/>
-        <v>4982.9471999999987</v>
+      <c r="E10" s="109">
+        <f t="shared" si="16"/>
+        <v>4666.5695999999989</v>
       </c>
       <c r="F10" s="6">
         <v>160</v>
       </c>
       <c r="G10" s="6">
-        <f t="shared" si="9"/>
-        <v>31.143419999999992</v>
+        <f t="shared" si="17"/>
+        <v>29.166059999999995</v>
       </c>
       <c r="H10" s="6">
         <v>9</v>
       </c>
       <c r="I10" s="6">
-        <f t="shared" si="10"/>
-        <v>3.4603799999999989</v>
+        <f t="shared" si="18"/>
+        <v>3.2406733333333326</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B11" s="114">
+      <c r="B11" s="109">
         <f>+K16</f>
-        <v>194646.37499999994</v>
+        <v>510406.04999999993</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B12" s="114">
+      <c r="B12" s="109">
         <f>+K28</f>
-        <v>186860.51999999996</v>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="116">
+      <c r="B13" s="111">
         <f>+K39</f>
-        <v>436007.87999999989</v>
-      </c>
-      <c r="E13" s="109" t="s">
+        <v>918730.88999999966</v>
+      </c>
+      <c r="E13" s="104" t="s">
         <v>141</v>
       </c>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="109"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="104"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B14" s="114">
-        <f>+K51</f>
-        <v>124573.67999999996</v>
-      </c>
-      <c r="E14" s="111" t="s">
+      <c r="B14" s="109">
+        <f>+K54</f>
+        <v>408324.83999999991</v>
+      </c>
+      <c r="E14" s="106" t="s">
         <v>136</v>
       </c>
-      <c r="F14" s="111" t="s">
+      <c r="F14" s="106" t="s">
         <v>137</v>
       </c>
-      <c r="G14" s="111" t="s">
+      <c r="G14" s="106" t="s">
         <v>138</v>
       </c>
-      <c r="H14" s="111" t="s">
+      <c r="H14" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="I14" s="111" t="s">
+      <c r="I14" s="106" t="s">
         <v>140</v>
       </c>
-      <c r="J14" s="111" t="s">
+      <c r="J14" s="106" t="s">
         <v>147</v>
       </c>
-      <c r="K14" s="111" t="s">
+      <c r="K14" s="106" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4078,1121 +4069,1175 @@
       <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="115">
+      <c r="B15" s="110">
         <f>SUM(B11:B14)</f>
-        <v>942088.45499999973</v>
-      </c>
-      <c r="E15" s="114">
-        <f t="shared" ref="E15:E23" si="11">+$C$3</f>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="F15" s="114">
+        <v>2216620.5599999996</v>
+      </c>
+      <c r="E15" s="109">
+        <f t="shared" ref="E15:E23" si="19">+$C$3</f>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="F15" s="109">
         <v>160</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" ref="G15:G46" si="12">+E15/F15</f>
-        <v>7.785854999999998</v>
-      </c>
-      <c r="H15" s="117">
+        <f t="shared" ref="G15:G47" si="20">+E15/F15</f>
+        <v>7.2915149999999986</v>
+      </c>
+      <c r="H15" s="112">
         <v>1</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" ref="I15:I46" si="13">+G15/H15</f>
-        <v>7.785854999999998</v>
-      </c>
-      <c r="J15" s="114">
-        <v>25000</v>
-      </c>
-      <c r="K15" s="114">
-        <f t="shared" ref="K15:K46" si="14">+J15*H15*I15</f>
-        <v>194646.37499999994</v>
+        <f t="shared" ref="I15:I47" si="21">+G15/H15</f>
+        <v>7.2915149999999986</v>
+      </c>
+      <c r="J15" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K15" s="109">
+        <f t="shared" ref="K15:K47" si="22">+J15*H15*I15</f>
+        <v>510406.04999999993</v>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="114">
-        <f t="shared" si="11"/>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="F16" s="114">
+      <c r="E16" s="109">
+        <f t="shared" si="19"/>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="F16" s="109">
         <v>160</v>
       </c>
       <c r="G16" s="6">
-        <f t="shared" si="12"/>
-        <v>7.785854999999998</v>
+        <f t="shared" si="20"/>
+        <v>7.2915149999999986</v>
       </c>
       <c r="H16" s="6">
         <v>2</v>
       </c>
       <c r="I16" s="6">
-        <f t="shared" si="13"/>
-        <v>3.892927499999999</v>
-      </c>
-      <c r="J16" s="114">
-        <v>25000</v>
-      </c>
-      <c r="K16" s="114">
-        <f t="shared" si="14"/>
-        <v>194646.37499999994</v>
+        <f t="shared" si="21"/>
+        <v>3.6457574999999993</v>
+      </c>
+      <c r="J16" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K16" s="109">
+        <f t="shared" si="22"/>
+        <v>510406.04999999993</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="E17" s="114">
-        <f t="shared" si="11"/>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="F17" s="114">
+      <c r="E17" s="109">
+        <f t="shared" si="19"/>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="F17" s="109">
         <v>160</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="12"/>
-        <v>7.785854999999998</v>
+        <f t="shared" si="20"/>
+        <v>7.2915149999999986</v>
       </c>
       <c r="H17" s="7">
         <v>3</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" si="13"/>
-        <v>2.5952849999999992</v>
-      </c>
-      <c r="J17" s="114">
-        <v>25000</v>
-      </c>
-      <c r="K17" s="114">
-        <f t="shared" si="14"/>
-        <v>194646.37499999994</v>
+        <f t="shared" si="21"/>
+        <v>2.4305049999999997</v>
+      </c>
+      <c r="J17" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K17" s="109">
+        <f t="shared" si="22"/>
+        <v>510406.04999999993</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="94" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="99" t="s">
+      <c r="B18" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="99" t="s">
+      <c r="C18" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="114">
-        <f t="shared" si="11"/>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="F18" s="114">
+      <c r="E18" s="109">
+        <f t="shared" si="19"/>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="F18" s="109">
         <v>160</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="12"/>
-        <v>7.785854999999998</v>
+        <f t="shared" si="20"/>
+        <v>7.2915149999999986</v>
       </c>
       <c r="H18" s="7">
         <v>4</v>
       </c>
       <c r="I18" s="6">
-        <f t="shared" si="13"/>
-        <v>1.9464637499999995</v>
-      </c>
-      <c r="J18" s="114">
-        <v>25000</v>
-      </c>
-      <c r="K18" s="114">
-        <f t="shared" si="14"/>
-        <v>194646.37499999994</v>
+        <f t="shared" si="21"/>
+        <v>1.8228787499999997</v>
+      </c>
+      <c r="J18" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K18" s="109">
+        <f t="shared" si="22"/>
+        <v>510406.04999999993</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B19" s="24">
-        <f>+H19</f>
-        <v>5</v>
-      </c>
-      <c r="C19" s="114">
-        <f>+I19</f>
-        <v>1.5571709999999996</v>
-      </c>
-      <c r="E19" s="114">
-        <f t="shared" si="11"/>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="F19" s="114">
+      <c r="B19" s="21">
+        <f>+H17</f>
+        <v>3</v>
+      </c>
+      <c r="C19" s="109">
+        <f>+I17</f>
+        <v>2.4305049999999997</v>
+      </c>
+      <c r="E19" s="109">
+        <f t="shared" si="19"/>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="F19" s="109">
         <v>160</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="12"/>
-        <v>7.785854999999998</v>
+        <f t="shared" si="20"/>
+        <v>7.2915149999999986</v>
       </c>
       <c r="H19" s="6">
         <v>5</v>
       </c>
       <c r="I19" s="6">
-        <f t="shared" si="13"/>
-        <v>1.5571709999999996</v>
-      </c>
-      <c r="J19" s="114">
-        <v>25000</v>
-      </c>
-      <c r="K19" s="114">
-        <f t="shared" si="14"/>
-        <v>194646.37499999994</v>
+        <f t="shared" si="21"/>
+        <v>1.4583029999999997</v>
+      </c>
+      <c r="J19" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K19" s="109">
+        <f t="shared" si="22"/>
+        <v>510406.04999999987</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="21">
         <f>+H28</f>
         <v>2</v>
       </c>
-      <c r="C20" s="114">
+      <c r="C20" s="109">
         <f>+I28</f>
-        <v>3.1143419999999993</v>
-      </c>
-      <c r="E20" s="114">
-        <f t="shared" si="11"/>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="F20" s="114">
+        <v>2.9166059999999994</v>
+      </c>
+      <c r="E20" s="109">
+        <f t="shared" si="19"/>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="F20" s="109">
         <v>160</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="12"/>
-        <v>7.785854999999998</v>
+        <f t="shared" si="20"/>
+        <v>7.2915149999999986</v>
       </c>
       <c r="H20" s="6">
         <v>6</v>
       </c>
       <c r="I20" s="6">
-        <f t="shared" si="13"/>
-        <v>1.2976424999999996</v>
-      </c>
-      <c r="J20" s="114">
-        <v>25000</v>
-      </c>
-      <c r="K20" s="114">
-        <f t="shared" si="14"/>
-        <v>194646.37499999994</v>
+        <f t="shared" si="21"/>
+        <v>1.2152524999999998</v>
+      </c>
+      <c r="J20" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K20" s="109">
+        <f t="shared" si="22"/>
+        <v>510406.04999999993</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="118">
+      <c r="B21" s="113">
         <f>+H47</f>
         <v>10</v>
       </c>
-      <c r="C21" s="116">
+      <c r="C21" s="111">
         <f>+I47</f>
-        <v>1.0900196999999996</v>
-      </c>
-      <c r="E21" s="114">
-        <f t="shared" si="11"/>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="F21" s="114">
+        <v>1.0208120999999997</v>
+      </c>
+      <c r="E21" s="109">
+        <f t="shared" si="19"/>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="F21" s="109">
         <v>160</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="12"/>
-        <v>7.785854999999998</v>
+        <f t="shared" si="20"/>
+        <v>7.2915149999999986</v>
       </c>
       <c r="H21" s="6">
         <v>7</v>
       </c>
       <c r="I21" s="6">
-        <f t="shared" si="13"/>
-        <v>1.1122649999999996</v>
-      </c>
-      <c r="J21" s="114">
-        <v>25000</v>
-      </c>
-      <c r="K21" s="114">
-        <f t="shared" si="14"/>
-        <v>194646.37499999994</v>
+        <f t="shared" si="21"/>
+        <v>1.0416449999999997</v>
+      </c>
+      <c r="J21" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K21" s="109">
+        <f t="shared" si="22"/>
+        <v>510406.04999999987</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="24">
-        <f>+H54</f>
+      <c r="B22" s="21">
+        <f>+H57</f>
         <v>5</v>
       </c>
-      <c r="C22" s="114">
-        <f>+I54</f>
-        <v>1.2457367999999998</v>
-      </c>
-      <c r="E22" s="114">
-        <f t="shared" si="11"/>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="F22" s="114">
+      <c r="C22" s="109">
+        <f>+I57</f>
+        <v>1.1666423999999997</v>
+      </c>
+      <c r="E22" s="109">
+        <f t="shared" si="19"/>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="F22" s="109">
         <v>160</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="12"/>
-        <v>7.785854999999998</v>
+        <f t="shared" si="20"/>
+        <v>7.2915149999999986</v>
       </c>
       <c r="H22" s="6">
         <v>8</v>
       </c>
       <c r="I22" s="6">
-        <f t="shared" si="13"/>
-        <v>0.97323187499999975</v>
-      </c>
-      <c r="J22" s="114">
-        <v>25000</v>
-      </c>
-      <c r="K22" s="114">
-        <f t="shared" si="14"/>
-        <v>194646.37499999994</v>
+        <f t="shared" si="21"/>
+        <v>0.91143937499999983</v>
+      </c>
+      <c r="J22" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K22" s="109">
+        <f t="shared" si="22"/>
+        <v>510406.04999999993</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="119">
+      <c r="B23" s="114">
         <f>SUM(B19:B22)</f>
-        <v>22</v>
-      </c>
-      <c r="C23" s="115">
+        <v>20</v>
+      </c>
+      <c r="C23" s="110">
         <f>SUM(C19:C22)</f>
-        <v>7.0072694999999978</v>
-      </c>
-      <c r="E23" s="114">
-        <f t="shared" si="11"/>
-        <v>1245.7367999999997</v>
-      </c>
-      <c r="F23" s="114">
+        <v>7.5345654999999985</v>
+      </c>
+      <c r="E23" s="109">
+        <f t="shared" si="19"/>
+        <v>1166.6423999999997</v>
+      </c>
+      <c r="F23" s="109">
         <v>160</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="12"/>
-        <v>7.785854999999998</v>
+        <f t="shared" si="20"/>
+        <v>7.2915149999999986</v>
       </c>
       <c r="H23" s="6">
         <v>9</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" si="13"/>
-        <v>0.86509499999999973</v>
-      </c>
-      <c r="J23" s="114">
-        <v>25000</v>
-      </c>
-      <c r="K23" s="114">
-        <f t="shared" si="14"/>
-        <v>194646.37499999994</v>
+        <f t="shared" si="21"/>
+        <v>0.81016833333333316</v>
+      </c>
+      <c r="J23" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K23" s="109">
+        <f t="shared" si="22"/>
+        <v>510406.04999999987</v>
       </c>
     </row>
     <row r="25">
-      <c r="E25" s="120" t="s">
+      <c r="E25" s="115" t="s">
         <v>142</v>
       </c>
-      <c r="F25" s="120"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="120"/>
-      <c r="I25" s="120"/>
-      <c r="J25" s="120"/>
-      <c r="K25" s="120"/>
+      <c r="F25" s="115"/>
+      <c r="G25" s="115"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="115"/>
+      <c r="K25" s="115"/>
     </row>
     <row r="26">
-      <c r="E26" s="111" t="s">
+      <c r="E26" s="106" t="s">
         <v>136</v>
       </c>
-      <c r="F26" s="111" t="s">
+      <c r="F26" s="106" t="s">
         <v>137</v>
       </c>
-      <c r="G26" s="111" t="s">
+      <c r="G26" s="106" t="s">
         <v>138</v>
       </c>
-      <c r="H26" s="111" t="s">
+      <c r="H26" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="I26" s="111" t="s">
+      <c r="I26" s="106" t="s">
         <v>140</v>
       </c>
-      <c r="J26" s="111" t="s">
+      <c r="J26" s="106" t="s">
         <v>150</v>
       </c>
-      <c r="K26" s="111" t="s">
+      <c r="K26" s="106" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="27">
-      <c r="E27" s="114">
-        <f t="shared" ref="E27:E35" si="15">+$C$4</f>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F27" s="114">
+      <c r="E27" s="109">
+        <f t="shared" ref="E27:E35" si="23">+$C$4</f>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F27" s="109">
         <v>160</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="12"/>
-        <v>6.2286839999999986</v>
-      </c>
-      <c r="H27" s="117">
+        <f t="shared" si="20"/>
+        <v>5.8332119999999987</v>
+      </c>
+      <c r="H27" s="112">
         <v>1</v>
       </c>
       <c r="I27" s="6">
-        <f t="shared" si="13"/>
-        <v>6.2286839999999986</v>
-      </c>
-      <c r="J27" s="114">
-        <v>30000</v>
-      </c>
-      <c r="K27" s="114">
-        <f t="shared" si="14"/>
-        <v>186860.51999999996</v>
+        <f t="shared" si="21"/>
+        <v>5.8332119999999987</v>
+      </c>
+      <c r="J27" s="109">
+        <v>65000</v>
+      </c>
+      <c r="K27" s="109">
+        <f t="shared" si="22"/>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="28">
-      <c r="E28" s="114">
-        <f t="shared" si="15"/>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F28" s="114">
+      <c r="E28" s="109">
+        <f t="shared" si="23"/>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F28" s="109">
         <v>160</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" si="12"/>
-        <v>6.2286839999999986</v>
+        <f t="shared" si="20"/>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H28" s="6">
         <v>2</v>
       </c>
       <c r="I28" s="6">
-        <f t="shared" si="13"/>
-        <v>3.1143419999999993</v>
-      </c>
-      <c r="J28" s="114">
-        <v>30000</v>
-      </c>
-      <c r="K28" s="114">
-        <f t="shared" si="14"/>
-        <v>186860.51999999996</v>
+        <f t="shared" si="21"/>
+        <v>2.9166059999999994</v>
+      </c>
+      <c r="J28" s="109">
+        <v>65000</v>
+      </c>
+      <c r="K28" s="109">
+        <f t="shared" si="22"/>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="29">
-      <c r="E29" s="114">
-        <f t="shared" si="15"/>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F29" s="114">
+      <c r="E29" s="109">
+        <f t="shared" si="23"/>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F29" s="109">
         <v>160</v>
       </c>
       <c r="G29" s="6">
-        <f t="shared" si="12"/>
-        <v>6.2286839999999986</v>
+        <f t="shared" si="20"/>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H29" s="7">
         <v>3</v>
       </c>
       <c r="I29" s="7">
-        <f t="shared" si="13"/>
-        <v>2.0762279999999995</v>
-      </c>
-      <c r="J29" s="114">
-        <v>30000</v>
-      </c>
-      <c r="K29" s="114">
-        <f t="shared" si="14"/>
-        <v>186860.51999999996</v>
+        <f t="shared" si="21"/>
+        <v>1.9444039999999996</v>
+      </c>
+      <c r="J29" s="109">
+        <v>65000</v>
+      </c>
+      <c r="K29" s="109">
+        <f t="shared" si="22"/>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="30">
-      <c r="E30" s="114">
-        <f t="shared" si="15"/>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F30" s="114">
+      <c r="E30" s="109">
+        <f t="shared" si="23"/>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F30" s="109">
         <v>160</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" si="12"/>
-        <v>6.2286839999999986</v>
+        <f t="shared" si="20"/>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H30" s="6">
         <v>4</v>
       </c>
       <c r="I30" s="6">
-        <f t="shared" si="13"/>
-        <v>1.5571709999999996</v>
-      </c>
-      <c r="J30" s="114">
-        <v>30000</v>
-      </c>
-      <c r="K30" s="114">
-        <f t="shared" si="14"/>
-        <v>186860.51999999996</v>
+        <f t="shared" si="21"/>
+        <v>1.4583029999999997</v>
+      </c>
+      <c r="J30" s="109">
+        <v>65000</v>
+      </c>
+      <c r="K30" s="109">
+        <f t="shared" si="22"/>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="31">
-      <c r="E31" s="114">
-        <f t="shared" si="15"/>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F31" s="114">
+      <c r="E31" s="109">
+        <f t="shared" si="23"/>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F31" s="109">
         <v>160</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" si="12"/>
-        <v>6.2286839999999986</v>
+        <f t="shared" si="20"/>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H31" s="6">
         <v>5</v>
       </c>
       <c r="I31" s="6">
-        <f t="shared" si="13"/>
-        <v>1.2457367999999998</v>
-      </c>
-      <c r="J31" s="114">
-        <v>30000</v>
-      </c>
-      <c r="K31" s="114">
-        <f t="shared" si="14"/>
-        <v>186860.51999999996</v>
+        <f t="shared" si="21"/>
+        <v>1.1666423999999997</v>
+      </c>
+      <c r="J31" s="109">
+        <v>65000</v>
+      </c>
+      <c r="K31" s="109">
+        <f t="shared" si="22"/>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="32">
-      <c r="E32" s="114">
-        <f t="shared" si="15"/>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F32" s="114">
+      <c r="E32" s="109">
+        <f t="shared" si="23"/>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F32" s="109">
         <v>160</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="12"/>
-        <v>6.2286839999999986</v>
+        <f t="shared" si="20"/>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H32" s="6">
         <v>6</v>
       </c>
       <c r="I32" s="6">
-        <f t="shared" si="13"/>
-        <v>1.0381139999999998</v>
-      </c>
-      <c r="J32" s="114">
-        <v>30000</v>
-      </c>
-      <c r="K32" s="114">
-        <f t="shared" si="14"/>
-        <v>186860.51999999996</v>
+        <f t="shared" si="21"/>
+        <v>0.97220199999999979</v>
+      </c>
+      <c r="J32" s="109">
+        <v>65000</v>
+      </c>
+      <c r="K32" s="109">
+        <f t="shared" si="22"/>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="33">
-      <c r="E33" s="114">
-        <f t="shared" si="15"/>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F33" s="114">
+      <c r="E33" s="109">
+        <f t="shared" si="23"/>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F33" s="109">
         <v>160</v>
       </c>
       <c r="G33" s="6">
-        <f t="shared" si="12"/>
-        <v>6.2286839999999986</v>
+        <f t="shared" si="20"/>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H33" s="6">
         <v>7</v>
       </c>
       <c r="I33" s="6">
-        <f t="shared" si="13"/>
-        <v>0.88981199999999983</v>
-      </c>
-      <c r="J33" s="114">
-        <v>30000</v>
-      </c>
-      <c r="K33" s="114">
-        <f t="shared" si="14"/>
-        <v>186860.51999999996</v>
+        <f t="shared" si="21"/>
+        <v>0.83331599999999983</v>
+      </c>
+      <c r="J33" s="109">
+        <v>65000</v>
+      </c>
+      <c r="K33" s="109">
+        <f t="shared" si="22"/>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="34">
-      <c r="E34" s="114">
-        <f t="shared" si="15"/>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F34" s="114">
+      <c r="E34" s="109">
+        <f t="shared" si="23"/>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F34" s="109">
         <v>160</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" si="12"/>
-        <v>6.2286839999999986</v>
+        <f t="shared" si="20"/>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H34" s="6">
         <v>8</v>
       </c>
       <c r="I34" s="6">
-        <f t="shared" si="13"/>
-        <v>0.77858549999999982</v>
-      </c>
-      <c r="J34" s="114">
-        <v>30000</v>
-      </c>
-      <c r="K34" s="114">
-        <f t="shared" si="14"/>
-        <v>186860.51999999996</v>
+        <f t="shared" si="21"/>
+        <v>0.72915149999999984</v>
+      </c>
+      <c r="J34" s="109">
+        <v>65000</v>
+      </c>
+      <c r="K34" s="109">
+        <f t="shared" si="22"/>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="35">
-      <c r="E35" s="114">
-        <f t="shared" si="15"/>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F35" s="114">
+      <c r="E35" s="109">
+        <f t="shared" si="23"/>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F35" s="109">
         <v>160</v>
       </c>
       <c r="G35" s="6">
-        <f t="shared" si="12"/>
-        <v>6.2286839999999986</v>
+        <f t="shared" si="20"/>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H35" s="6">
         <v>9</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" si="13"/>
-        <v>0.6920759999999998</v>
-      </c>
-      <c r="J35" s="114">
-        <v>30000</v>
-      </c>
-      <c r="K35" s="114">
-        <f t="shared" si="14"/>
-        <v>186860.51999999996</v>
+        <f t="shared" si="21"/>
+        <v>0.64813466666666653</v>
+      </c>
+      <c r="J35" s="109">
+        <v>65000</v>
+      </c>
+      <c r="K35" s="109">
+        <f t="shared" si="22"/>
+        <v>379158.77999999991</v>
       </c>
     </row>
     <row r="37">
-      <c r="E37" s="120" t="s">
+      <c r="E37" s="115" t="s">
         <v>143</v>
       </c>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="120"/>
-      <c r="J37" s="120"/>
-      <c r="K37" s="120"/>
+      <c r="F37" s="115"/>
+      <c r="G37" s="115"/>
+      <c r="H37" s="115"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="115"/>
+      <c r="K37" s="115"/>
     </row>
     <row r="38">
-      <c r="E38" s="111" t="s">
+      <c r="E38" s="106" t="s">
         <v>136</v>
       </c>
-      <c r="F38" s="111" t="s">
+      <c r="F38" s="106" t="s">
         <v>137</v>
       </c>
-      <c r="G38" s="111" t="s">
+      <c r="G38" s="106" t="s">
         <v>138</v>
       </c>
-      <c r="H38" s="111" t="s">
+      <c r="H38" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="111" t="s">
+      <c r="I38" s="106" t="s">
         <v>140</v>
       </c>
-      <c r="J38" s="111" t="s">
+      <c r="J38" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="K38" s="111" t="s">
+      <c r="K38" s="106" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="39">
-      <c r="E39" s="114">
-        <f t="shared" ref="E39:E46" si="16">+$C$5</f>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="F39" s="114">
+      <c r="E39" s="109">
+        <f t="shared" ref="E39:E47" si="24">+$C$5</f>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F39" s="109">
         <v>160</v>
       </c>
       <c r="G39" s="6">
-        <f t="shared" si="12"/>
-        <v>10.900196999999997</v>
-      </c>
-      <c r="H39" s="117">
+        <f t="shared" si="20"/>
+        <v>10.208120999999997</v>
+      </c>
+      <c r="H39" s="112">
         <v>2</v>
       </c>
       <c r="I39" s="6">
-        <f t="shared" si="13"/>
-        <v>5.4500984999999984</v>
-      </c>
-      <c r="J39" s="114">
-        <v>40000</v>
-      </c>
-      <c r="K39" s="114">
-        <f t="shared" si="14"/>
-        <v>436007.87999999989</v>
+        <f t="shared" si="21"/>
+        <v>5.1040604999999983</v>
+      </c>
+      <c r="J39" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K39" s="109">
+        <f t="shared" si="22"/>
+        <v>918730.88999999966</v>
       </c>
     </row>
     <row r="40">
-      <c r="E40" s="114">
-        <f t="shared" si="16"/>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="F40" s="114">
+      <c r="E40" s="109">
+        <f t="shared" si="24"/>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F40" s="109">
         <v>160</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" si="12"/>
-        <v>10.900196999999997</v>
+        <f t="shared" si="20"/>
+        <v>10.208120999999997</v>
       </c>
       <c r="H40" s="6">
         <v>3</v>
       </c>
       <c r="I40" s="6">
-        <f t="shared" si="13"/>
-        <v>3.6333989999999989</v>
-      </c>
-      <c r="J40" s="114">
-        <v>40000</v>
-      </c>
-      <c r="K40" s="114">
-        <f t="shared" si="14"/>
-        <v>436007.87999999989</v>
+        <f t="shared" si="21"/>
+        <v>3.402706999999999</v>
+      </c>
+      <c r="J40" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K40" s="109">
+        <f t="shared" si="22"/>
+        <v>918730.88999999978</v>
       </c>
     </row>
     <row r="41">
-      <c r="E41" s="114">
-        <f t="shared" si="16"/>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="F41" s="114">
+      <c r="E41" s="109">
+        <f t="shared" si="24"/>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F41" s="109">
         <v>160</v>
       </c>
       <c r="G41" s="6">
-        <f t="shared" si="12"/>
-        <v>10.900196999999997</v>
+        <f t="shared" si="20"/>
+        <v>10.208120999999997</v>
       </c>
       <c r="H41" s="7">
         <v>4</v>
       </c>
       <c r="I41" s="7">
-        <f t="shared" si="13"/>
-        <v>2.7250492499999992</v>
-      </c>
-      <c r="J41" s="114">
-        <v>40000</v>
-      </c>
-      <c r="K41" s="114">
-        <f t="shared" si="14"/>
-        <v>436007.87999999989</v>
+        <f t="shared" si="21"/>
+        <v>2.5520302499999992</v>
+      </c>
+      <c r="J41" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K41" s="109">
+        <f t="shared" si="22"/>
+        <v>918730.88999999966</v>
       </c>
     </row>
     <row r="42">
-      <c r="E42" s="114">
-        <f t="shared" si="16"/>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="F42" s="114">
+      <c r="E42" s="109">
+        <f t="shared" si="24"/>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F42" s="109">
         <v>160</v>
       </c>
       <c r="G42" s="6">
-        <f t="shared" si="12"/>
-        <v>10.900196999999997</v>
+        <f t="shared" si="20"/>
+        <v>10.208120999999997</v>
       </c>
       <c r="H42" s="6">
         <v>5</v>
       </c>
       <c r="I42" s="6">
-        <f t="shared" si="13"/>
-        <v>2.1800393999999992</v>
-      </c>
-      <c r="J42" s="114">
-        <v>40000</v>
-      </c>
-      <c r="K42" s="114">
-        <f t="shared" si="14"/>
-        <v>436007.87999999983</v>
+        <f t="shared" si="21"/>
+        <v>2.0416241999999993</v>
+      </c>
+      <c r="J42" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K42" s="109">
+        <f t="shared" si="22"/>
+        <v>918730.88999999966</v>
       </c>
     </row>
     <row r="43">
-      <c r="E43" s="114">
-        <f t="shared" si="16"/>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="F43" s="114">
+      <c r="E43" s="109">
+        <f t="shared" si="24"/>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F43" s="109">
         <v>160</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" si="12"/>
-        <v>10.900196999999997</v>
+        <f t="shared" si="20"/>
+        <v>10.208120999999997</v>
       </c>
       <c r="H43" s="6">
         <v>6</v>
       </c>
       <c r="I43" s="6">
-        <f t="shared" si="13"/>
-        <v>1.8166994999999995</v>
-      </c>
-      <c r="J43" s="114">
-        <v>40000</v>
-      </c>
-      <c r="K43" s="114">
-        <f t="shared" si="14"/>
-        <v>436007.87999999989</v>
+        <f t="shared" si="21"/>
+        <v>1.7013534999999995</v>
+      </c>
+      <c r="J43" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K43" s="109">
+        <f t="shared" si="22"/>
+        <v>918730.88999999978</v>
       </c>
     </row>
     <row r="44">
-      <c r="E44" s="114">
-        <f t="shared" si="16"/>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="F44" s="114">
+      <c r="E44" s="109">
+        <f t="shared" si="24"/>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F44" s="109">
         <v>160</v>
       </c>
       <c r="G44" s="6">
-        <f t="shared" si="12"/>
-        <v>10.900196999999997</v>
+        <f t="shared" si="20"/>
+        <v>10.208120999999997</v>
       </c>
       <c r="H44" s="6">
         <v>7</v>
       </c>
       <c r="I44" s="6">
-        <f t="shared" si="13"/>
-        <v>1.5571709999999996</v>
-      </c>
-      <c r="J44" s="114">
-        <v>40000</v>
-      </c>
-      <c r="K44" s="114">
-        <f t="shared" si="14"/>
-        <v>436007.87999999989</v>
+        <f t="shared" si="21"/>
+        <v>1.4583029999999995</v>
+      </c>
+      <c r="J44" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K44" s="109">
+        <f t="shared" si="22"/>
+        <v>918730.88999999966</v>
       </c>
     </row>
     <row r="45">
-      <c r="E45" s="114">
-        <f t="shared" si="16"/>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="F45" s="114">
+      <c r="E45" s="109">
+        <f t="shared" si="24"/>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F45" s="109">
         <v>160</v>
       </c>
       <c r="G45" s="6">
-        <f t="shared" si="12"/>
-        <v>10.900196999999997</v>
+        <f t="shared" si="20"/>
+        <v>10.208120999999997</v>
       </c>
       <c r="H45" s="6">
         <v>8</v>
       </c>
       <c r="I45" s="6">
-        <f t="shared" si="13"/>
-        <v>1.3625246249999996</v>
-      </c>
-      <c r="J45" s="114">
-        <v>40000</v>
-      </c>
-      <c r="K45" s="114">
-        <f t="shared" si="14"/>
-        <v>436007.87999999989</v>
+        <f t="shared" si="21"/>
+        <v>1.2760151249999996</v>
+      </c>
+      <c r="J45" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K45" s="109">
+        <f t="shared" si="22"/>
+        <v>918730.88999999966</v>
       </c>
     </row>
     <row r="46">
-      <c r="E46" s="114">
-        <f t="shared" si="16"/>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="F46" s="114">
+      <c r="E46" s="109">
+        <f t="shared" si="24"/>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F46" s="109">
         <v>160</v>
       </c>
       <c r="G46" s="6">
-        <f t="shared" si="12"/>
-        <v>10.900196999999997</v>
+        <f t="shared" si="20"/>
+        <v>10.208120999999997</v>
       </c>
       <c r="H46" s="6">
         <v>9</v>
       </c>
       <c r="I46" s="6">
-        <f t="shared" si="13"/>
-        <v>1.2111329999999996</v>
-      </c>
-      <c r="J46" s="114">
-        <v>40000</v>
-      </c>
-      <c r="K46" s="114">
-        <f t="shared" si="14"/>
-        <v>436007.87999999983</v>
+        <f t="shared" si="21"/>
+        <v>1.1342356666666662</v>
+      </c>
+      <c r="J46" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K46" s="109">
+        <f t="shared" si="22"/>
+        <v>918730.88999999966</v>
       </c>
     </row>
     <row r="47" ht="14.25">
-      <c r="E47" s="114">
-        <f>+$C$5</f>
-        <v>1744.0315199999995</v>
-      </c>
-      <c r="F47" s="114">
+      <c r="E47" s="109">
+        <f t="shared" si="24"/>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F47" s="109">
         <v>160</v>
       </c>
       <c r="G47" s="6">
-        <f>+E47/F47</f>
-        <v>10.900196999999997</v>
+        <f t="shared" si="20"/>
+        <v>10.208120999999997</v>
       </c>
       <c r="H47" s="6">
         <v>10</v>
       </c>
       <c r="I47" s="6">
-        <f>+G47/H47</f>
-        <v>1.0900196999999996</v>
-      </c>
-      <c r="J47" s="114">
-        <v>40000</v>
-      </c>
-      <c r="K47" s="114">
-        <f>+J47*H47*I47</f>
-        <v>436007.87999999983</v>
+        <f t="shared" si="21"/>
+        <v>1.0208120999999997</v>
+      </c>
+      <c r="J47" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K47" s="109">
+        <f t="shared" si="22"/>
+        <v>918730.88999999966</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="E48" s="109">
+        <f>+$C$5</f>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F48" s="109">
+        <v>160</v>
+      </c>
+      <c r="G48" s="6">
+        <f>+E48/F48</f>
+        <v>10.208120999999997</v>
+      </c>
+      <c r="H48" s="6">
+        <v>11</v>
+      </c>
+      <c r="I48" s="6">
+        <f>+G48/H48</f>
+        <v>0.9280109999999997</v>
+      </c>
+      <c r="J48" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K48" s="109">
+        <f>+J48*H48*I48</f>
+        <v>918730.88999999966</v>
       </c>
     </row>
     <row r="49">
-      <c r="E49" s="120" t="s">
+      <c r="E49" s="109">
+        <f>+$C$5</f>
+        <v>1633.2993599999995</v>
+      </c>
+      <c r="F49" s="109">
+        <v>160</v>
+      </c>
+      <c r="G49" s="6">
+        <f>+E49/F49</f>
+        <v>10.208120999999997</v>
+      </c>
+      <c r="H49" s="6">
+        <v>12</v>
+      </c>
+      <c r="I49" s="6">
+        <f>+G49/H49</f>
+        <v>0.85067674999999976</v>
+      </c>
+      <c r="J49" s="109">
+        <v>90000</v>
+      </c>
+      <c r="K49" s="109">
+        <f>+J49*H49*I49</f>
+        <v>918730.88999999978</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="F49" s="120"/>
-      <c r="G49" s="120"/>
-      <c r="H49" s="120"/>
-      <c r="I49" s="120"/>
-      <c r="J49" s="120"/>
-      <c r="K49" s="120"/>
-    </row>
-    <row r="50">
-      <c r="E50" s="111" t="s">
+      <c r="F52" s="115"/>
+      <c r="G52" s="115"/>
+      <c r="H52" s="115"/>
+      <c r="I52" s="115"/>
+      <c r="J52" s="115"/>
+      <c r="K52" s="115"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="106" t="s">
         <v>136</v>
       </c>
-      <c r="F50" s="111" t="s">
+      <c r="F53" s="106" t="s">
         <v>137</v>
       </c>
-      <c r="G50" s="111" t="s">
+      <c r="G53" s="106" t="s">
         <v>138</v>
       </c>
-      <c r="H50" s="111" t="s">
+      <c r="H53" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="I50" s="111" t="s">
+      <c r="I53" s="106" t="s">
         <v>140</v>
       </c>
-      <c r="J50" s="111" t="s">
+      <c r="J53" s="106" t="s">
         <v>153</v>
       </c>
-      <c r="K50" s="111" t="s">
+      <c r="K53" s="106" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="51">
-      <c r="E51" s="114">
+    <row r="54">
+      <c r="E54" s="109">
         <f>+$C$6</f>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F51" s="6">
-        <v>160</v>
-      </c>
-      <c r="G51" s="6">
-        <f>+E51/F51</f>
-        <v>6.2286839999999986</v>
-      </c>
-      <c r="H51" s="117">
-        <v>2</v>
-      </c>
-      <c r="I51" s="6">
-        <f>+G51/H51</f>
-        <v>3.1143419999999993</v>
-      </c>
-      <c r="J51" s="114">
-        <v>20000</v>
-      </c>
-      <c r="K51" s="114">
-        <f>+J51*H51*I51</f>
-        <v>124573.67999999996</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="E52" s="114">
-        <f>+$C$6</f>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F52" s="6">
-        <v>160</v>
-      </c>
-      <c r="G52" s="6">
-        <f>+E52/F52</f>
-        <v>6.2286839999999986</v>
-      </c>
-      <c r="H52" s="6">
-        <v>3</v>
-      </c>
-      <c r="I52" s="6">
-        <f>+G52/H52</f>
-        <v>2.0762279999999995</v>
-      </c>
-      <c r="J52" s="114">
-        <v>20000</v>
-      </c>
-      <c r="K52" s="114">
-        <f>+J52*H52*I52</f>
-        <v>124573.67999999996</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="E53" s="114">
-        <f>+$C$6</f>
-        <v>996.58943999999974</v>
-      </c>
-      <c r="F53" s="6">
-        <v>160</v>
-      </c>
-      <c r="G53" s="6">
-        <f>+E53/F53</f>
-        <v>6.2286839999999986</v>
-      </c>
-      <c r="H53" s="6">
-        <v>4</v>
-      </c>
-      <c r="I53" s="6">
-        <f>+G53/H53</f>
-        <v>1.5571709999999996</v>
-      </c>
-      <c r="J53" s="114">
-        <v>20000</v>
-      </c>
-      <c r="K53" s="114">
-        <f>+J53*H53*I53</f>
-        <v>124573.67999999996</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="E54" s="114">
-        <f>+$C$6</f>
-        <v>996.58943999999974</v>
+        <v>933.31391999999983</v>
       </c>
       <c r="F54" s="6">
         <v>160</v>
       </c>
       <c r="G54" s="6">
         <f>+E54/F54</f>
-        <v>6.2286839999999986</v>
-      </c>
-      <c r="H54" s="7">
-        <v>5</v>
-      </c>
-      <c r="I54" s="7">
+        <v>5.8332119999999987</v>
+      </c>
+      <c r="H54" s="112">
+        <v>2</v>
+      </c>
+      <c r="I54" s="6">
         <f>+G54/H54</f>
-        <v>1.2457367999999998</v>
-      </c>
-      <c r="J54" s="114">
-        <v>20000</v>
-      </c>
-      <c r="K54" s="114">
+        <v>2.9166059999999994</v>
+      </c>
+      <c r="J54" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K54" s="109">
         <f>+J54*H54*I54</f>
-        <v>124573.67999999998</v>
+        <v>408324.83999999991</v>
       </c>
     </row>
     <row r="55">
-      <c r="E55" s="114">
+      <c r="E55" s="109">
         <f>+$C$6</f>
-        <v>996.58943999999974</v>
+        <v>933.31391999999983</v>
       </c>
       <c r="F55" s="6">
         <v>160</v>
       </c>
       <c r="G55" s="6">
         <f>+E55/F55</f>
-        <v>6.2286839999999986</v>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H55" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I55" s="6">
         <f>+G55/H55</f>
-        <v>1.0381139999999998</v>
-      </c>
-      <c r="J55" s="114">
-        <v>20000</v>
-      </c>
-      <c r="K55" s="114">
+        <v>1.9444039999999996</v>
+      </c>
+      <c r="J55" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K55" s="109">
         <f>+J55*H55*I55</f>
-        <v>124573.67999999996</v>
+        <v>408324.83999999991</v>
       </c>
     </row>
     <row r="56">
-      <c r="E56" s="114">
+      <c r="E56" s="109">
         <f>+$C$6</f>
-        <v>996.58943999999974</v>
+        <v>933.31391999999983</v>
       </c>
       <c r="F56" s="6">
         <v>160</v>
       </c>
       <c r="G56" s="6">
         <f>+E56/F56</f>
-        <v>6.2286839999999986</v>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H56" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I56" s="6">
         <f>+G56/H56</f>
-        <v>0.88981199999999983</v>
-      </c>
-      <c r="J56" s="114">
-        <v>20000</v>
-      </c>
-      <c r="K56" s="114">
+        <v>1.4583029999999997</v>
+      </c>
+      <c r="J56" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K56" s="109">
         <f>+J56*H56*I56</f>
-        <v>124573.67999999998</v>
+        <v>408324.83999999991</v>
       </c>
     </row>
     <row r="57">
-      <c r="E57" s="114">
+      <c r="E57" s="109">
         <f>+$C$6</f>
-        <v>996.58943999999974</v>
+        <v>933.31391999999983</v>
       </c>
       <c r="F57" s="6">
         <v>160</v>
       </c>
       <c r="G57" s="6">
         <f>+E57/F57</f>
-        <v>6.2286839999999986</v>
-      </c>
-      <c r="H57" s="6">
-        <v>8</v>
-      </c>
-      <c r="I57" s="6">
+        <v>5.8332119999999987</v>
+      </c>
+      <c r="H57" s="7">
+        <v>5</v>
+      </c>
+      <c r="I57" s="7">
         <f>+G57/H57</f>
-        <v>0.77858549999999982</v>
-      </c>
-      <c r="J57" s="114">
-        <v>20000</v>
-      </c>
-      <c r="K57" s="114">
+        <v>1.1666423999999997</v>
+      </c>
+      <c r="J57" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K57" s="109">
         <f>+J57*H57*I57</f>
-        <v>124573.67999999996</v>
+        <v>408324.83999999991</v>
       </c>
     </row>
     <row r="58" ht="14.25">
-      <c r="E58" s="114">
+      <c r="E58" s="109">
         <f>+$C$6</f>
-        <v>996.58943999999974</v>
+        <v>933.31391999999983</v>
       </c>
       <c r="F58" s="6">
         <v>160</v>
       </c>
       <c r="G58" s="6">
         <f>+E58/F58</f>
-        <v>6.2286839999999986</v>
+        <v>5.8332119999999987</v>
       </c>
       <c r="H58" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I58" s="6">
         <f>+G58/H58</f>
-        <v>0.6920759999999998</v>
-      </c>
-      <c r="J58" s="114">
-        <v>20000</v>
-      </c>
-      <c r="K58" s="114">
+        <v>0.97220199999999979</v>
+      </c>
+      <c r="J58" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K58" s="109">
         <f>+J58*H58*I58</f>
-        <v>124573.67999999996</v>
+        <v>408324.83999999991</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="E59" s="109">
+        <f>+$C$6</f>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F59" s="6">
+        <v>160</v>
+      </c>
+      <c r="G59" s="6">
+        <f>+E59/F59</f>
+        <v>5.8332119999999987</v>
+      </c>
+      <c r="H59" s="6">
+        <v>7</v>
+      </c>
+      <c r="I59" s="6">
+        <f>+G59/H59</f>
+        <v>0.83331599999999983</v>
+      </c>
+      <c r="J59" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K59" s="109">
+        <f>+J59*H59*I59</f>
+        <v>408324.83999999991</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="E60" s="109">
+        <f>+$C$6</f>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F60" s="6">
+        <v>160</v>
+      </c>
+      <c r="G60" s="6">
+        <f>+E60/F60</f>
+        <v>5.8332119999999987</v>
+      </c>
+      <c r="H60" s="6">
+        <v>8</v>
+      </c>
+      <c r="I60" s="6">
+        <f>+G60/H60</f>
+        <v>0.72915149999999984</v>
+      </c>
+      <c r="J60" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K60" s="109">
+        <f>+J60*H60*I60</f>
+        <v>408324.83999999991</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="E61" s="109">
+        <f>+$C$6</f>
+        <v>933.31391999999983</v>
+      </c>
+      <c r="F61" s="6">
+        <v>160</v>
+      </c>
+      <c r="G61" s="6">
+        <f>+E61/F61</f>
+        <v>5.8332119999999987</v>
+      </c>
+      <c r="H61" s="6">
+        <v>9</v>
+      </c>
+      <c r="I61" s="6">
+        <f>+G61/H61</f>
+        <v>0.64813466666666653</v>
+      </c>
+      <c r="J61" s="109">
+        <v>70000</v>
+      </c>
+      <c r="K61" s="109">
+        <f>+J61*H61*I61</f>
+        <v>408324.83999999991</v>
       </c>
     </row>
   </sheetData>
@@ -5201,7 +5246,7 @@
     <mergeCell ref="E13:K13"/>
     <mergeCell ref="E25:K25"/>
     <mergeCell ref="E37:K37"/>
-    <mergeCell ref="E49:K49"/>
+    <mergeCell ref="E52:K52"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
